--- a/output/pdf_financials_xlsx/BGD.xlsx
+++ b/output/pdf_financials_xlsx/BGD.xlsx
@@ -5024,10 +5024,10 @@
         <v>0.472646</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0.545696</v>
+        <v>0.760831</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.845512</v>
       </c>
       <c r="E92" s="3" t="n">
         <v>0.845512</v>
@@ -6268,7 +6268,7 @@
         <v>0</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0.051</v>
+        <v>0</v>
       </c>
       <c r="H118" s="3" t="n">
         <v>0</v>
@@ -15042,7 +15042,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>-</t>
@@ -16516,7 +16520,11 @@
           <t>Share-Based Payments Reserve</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>-</t>
@@ -25014,7 +25022,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr"/>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E210" t="inlineStr">
         <is>
           <t>-</t>
@@ -26574,7 +26586,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr"/>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E228" t="inlineStr">
         <is>
           <t>-</t>
@@ -40399,10 +40415,10 @@
         </is>
       </c>
       <c r="J389" s="5" t="n">
-        <v>0.101582</v>
+        <v>-0.101582</v>
       </c>
       <c r="K389" s="5" t="n">
-        <v>0.176161</v>
+        <v>-0.176161</v>
       </c>
       <c r="L389" t="inlineStr">
         <is>
@@ -42596,16 +42612,16 @@
         </is>
       </c>
       <c r="G415" s="5" t="n">
-        <v>0.497475</v>
+        <v>-0.497475</v>
       </c>
       <c r="H415" s="5" t="n">
-        <v>3.977695</v>
+        <v>-3.977695</v>
       </c>
       <c r="I415" s="5" t="n">
-        <v>0.18602</v>
+        <v>-0.18602</v>
       </c>
       <c r="J415" s="5" t="n">
-        <v>0.101582</v>
+        <v>-0.101582</v>
       </c>
       <c r="K415" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/BGD.xlsx
+++ b/output/pdf_financials_xlsx/BGD.xlsx
@@ -939,19 +939,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.000763</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.001391</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000411</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-5.5e-05</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-7.3e-05</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -1732,19 +1732,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.121561</v>
+        <v>-1.122324</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.933151</v>
+        <v>-0.934542</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.497501</v>
+        <v>0.497912</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>4.209695</v>
+        <v>4.20975</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.18602</v>
+        <v>0.186093</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-0.101582</v>
@@ -1830,19 +1830,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.121561</v>
+        <v>-1.122324</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.931899</v>
+        <v>-0.93329</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.500698</v>
+        <v>0.501109</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>4.210735</v>
+        <v>4.21079</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.186779</v>
+        <v>0.186852</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-0.101513</v>
@@ -2089,34 +2089,34 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.364186</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.170463</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.038501</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.006925</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.005266</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.008429000000000001</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.000123</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.06639399999999999</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.379396</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.127875</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>0.243316</v>
@@ -2128,7 +2128,7 @@
         <v>0.342471</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>1.252691</v>
       </c>
     </row>
     <row r="35">
@@ -2187,34 +2187,34 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.364186</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.170463</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.038501</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.006925</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.005266</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.008429000000000001</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.000123</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.0045</v>
+        <v>0.070894</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.00135</v>
+        <v>0.380746</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.00435</v>
+        <v>0.132225</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>0.618916</v>
@@ -2226,7 +2226,7 @@
         <v>0.442824</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.263142</v>
+        <v>1.515833</v>
       </c>
     </row>
     <row r="37">
@@ -2775,34 +2775,34 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.364186</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.338075</v>
+        <v>0.167612</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.042353</v>
+        <v>0.003852</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.010777</v>
+        <v>0.003852</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.005266</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.008429000000000001</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.000123</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.242873</v>
+        <v>0.176479</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.379396</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.136375</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>0.079164</v>
@@ -2814,7 +2814,7 @@
         <v>0.104284</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>1.365859</v>
+        <v>0.113168</v>
       </c>
     </row>
     <row r="49">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -9886,7 +9886,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -11766,7 +11766,11 @@
           <t>Reclamation deposit 7</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
@@ -12560,7 +12564,11 @@
           <t>Reclamation deposits 5</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
@@ -13672,7 +13680,11 @@
           <t>Reclamation deposits 5</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>-</t>
@@ -15132,7 +15144,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -15568,7 +15580,11 @@
           <t>Reclamation Deposits</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>-</t>
@@ -16862,7 +16878,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E114" s="5" t="n">
@@ -17382,7 +17398,11 @@
           <t>Reclamation deposit (Note 7) 12,000</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E120" s="5" t="n">
         <v>0.0035</v>
       </c>
@@ -30040,7 +30060,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr"/>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E268" t="inlineStr">
         <is>
           <t>-</t>
@@ -32638,7 +32662,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D298" t="inlineStr"/>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E298" t="inlineStr">
         <is>
           <t>-</t>
@@ -42342,7 +42370,7 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
@@ -46954,7 +46982,7 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
@@ -49278,7 +49306,7 @@
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E493" s="5" t="n">

--- a/output/pdf_financials_xlsx/BGD.xlsx
+++ b/output/pdf_financials_xlsx/BGD.xlsx
@@ -694,22 +694,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.102714</v>
+        <v>0.130435</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.049102</v>
+        <v>0.081898</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.06794699999999999</v>
+        <v>0.095593</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.024748</v>
+        <v>0.035079</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.011708</v>
+        <v>0.014736</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.110081</v>
+        <v>0.111172</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>0.115688</v>
@@ -841,7 +841,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.116479</v>
+        <v>0.1442</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>0.953321</v>
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.116479</v>
+        <v>-0.1442</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>-0.953321</v>
@@ -5937,7 +5937,7 @@
         <v>0</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>0</v>
+        <v>-0.00236</v>
       </c>
       <c r="L111" s="3" t="n">
         <v>0</v>
@@ -7092,7 +7092,7 @@
         <v>0</v>
       </c>
       <c r="K134" s="3" t="n">
-        <v>0</v>
+        <v>-0.00236</v>
       </c>
       <c r="L134" s="3" t="n">
         <v>0</v>
@@ -7141,7 +7141,7 @@
         <v>-0.269831</v>
       </c>
       <c r="K135" s="3" t="n">
-        <v>-0.249161</v>
+        <v>-0.251521</v>
       </c>
       <c r="L135" s="3" t="n">
         <v>-0.366412</v>
@@ -20368,7 +20368,11 @@
           <t>Issuance of units shares under a flow-through private placement 9</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E155" t="inlineStr">
         <is>
           <t>-</t>
@@ -21424,7 +21428,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr"/>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E168" t="inlineStr">
         <is>
           <t>-</t>
@@ -21684,7 +21692,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E171" t="inlineStr">
         <is>
           <t>-</t>
@@ -27036,7 +27048,11 @@
           <t>Deferred tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr">
         <is>
           <t>-</t>
@@ -28244,7 +28260,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr"/>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E247" t="inlineStr">
         <is>
           <t>-</t>
@@ -31628,7 +31648,11 @@
           <t>Deferred tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D286" t="inlineStr"/>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E286" s="5" t="n">
         <v>-0.008189999999999999</v>
       </c>
@@ -32926,7 +32950,11 @@
           <t>Proceeds from share issuances</t>
         </is>
       </c>
-      <c r="D301" t="inlineStr"/>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E301" s="5" t="n">
         <v>1.035</v>
       </c>
@@ -39984,7 +40012,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D384" t="inlineStr"/>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E384" t="inlineStr">
         <is>
           <t>-</t>
@@ -41950,7 +41982,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D407" t="inlineStr"/>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E407" t="inlineStr">
         <is>
           <t>-</t>
@@ -46376,7 +46412,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D459" t="inlineStr"/>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E459" t="inlineStr">
         <is>
           <t>-</t>
@@ -48532,7 +48572,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D484" t="inlineStr"/>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E484" s="5" t="n">
         <v>0.027721</v>
       </c>
